--- a/results/Int Task Remove ACC -0.1/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC -0.1/Rando_3_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7180630193494633</v>
+        <v>0.7003283636714046</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7180630193494633</v>
+        <v>0.7142569305807953</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7180630193494633</v>
+        <v>0.7142569305807953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7232554189496061</v>
+        <v>0.7257121846428783</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7321928288527858</v>
+        <v>0.7230315456891256</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7325162283779798</v>
+        <v>0.7259820492579575</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7359831004889197</v>
+        <v>0.7260280406125561</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7249047808621456</v>
+        <v>0.7255350327584982</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7260604048991257</v>
+        <v>0.7215140743278692</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7286566046991971</v>
+        <v>0.7113757790546125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7271233162054067</v>
+        <v>0.7051581859257694</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7267381081930799</v>
+        <v>0.7116373700926738</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7284251878832004</v>
+        <v>0.7122690820320294</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7159530138694352</v>
+        <v>0.6828093076768088</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7033112315268059</v>
+        <v>0.6828093076768088</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6963239523948113</v>
+        <v>0.6837568755858423</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6787362743790681</v>
+        <v>0.723232058261556</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6240978150943139</v>
+        <v>0.6891875055359964</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6237126070819872</v>
+        <v>0.6833091290648814</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6237126070819872</v>
+        <v>0.7141393971190431</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6216938542896551</v>
+        <v>0.7110961808195124</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6218325583749527</v>
+        <v>0.711650997160703</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5997686318521035</v>
+        <v>0.6632143138722579</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5953082004775314</v>
+        <v>0.66767474524683</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5935819429668268</v>
+        <v>0.6426844058647008</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5821108717722099</v>
+        <v>0.6389325820276494</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6089661727503414</v>
+        <v>0.6305967098417605</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6085425169389322</v>
+        <v>0.6442176943584912</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5811942081067428</v>
+        <v>0.6456047352114678</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5805542225903694</v>
+        <v>0.6438558470342146</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5404638751293355</v>
+        <v>0.6450190146267109</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5367964904459652</v>
+        <v>0.6443873026873551</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.49048927987759</v>
+        <v>0.5985874570625687</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4942335601591252</v>
+        <v>0.572387228711843</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4838404873818217</v>
+        <v>0.5709466529487515</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5001000129457146</v>
+        <v>0.593413794680966</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5058389553100304</v>
+        <v>0.6021175977036444</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4988592197335519</v>
+        <v>0.594822006157488</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4920641795969697</v>
+        <v>0.5878023627389239</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4817487324393327</v>
+        <v>0.5297948542244397</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4527503316731022</v>
+        <v>0.5072620105570842</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4555071362035183</v>
+        <v>0.496022356178464</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4213328829911804</v>
+        <v>0.496022356178464</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4087816233147453</v>
+        <v>0.4785266608719182</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.3805475550606551</v>
+        <v>0.4795895721781993</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.3613187887093902</v>
+        <v>0.4809917001422082</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.3356485559688018</v>
+        <v>0.5142923609576715</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.3508020989578213</v>
+        <v>0.5384828401145842</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.348876058896188</v>
+        <v>0.525578736712392</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.348876058896188</v>
+        <v>0.5347543769655829</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.3304719735011929</v>
+        <v>0.5005115017320977</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.2879625781244677</v>
+        <v>0.4014186264499444</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.2668544930876697</v>
+        <v>0.3892155870297567</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.2734716513183701</v>
+        <v>0.394594142112799</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.2725240834093366</v>
+        <v>0.4282581102955419</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.3240244235993564</v>
+        <v>0.4096301516400663</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.3235314157452984</v>
+        <v>0.4180044716250376</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3390543496141107</v>
+        <v>0.4094062783795859</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3484908508838614</v>
+        <v>0.5239821796884657</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.3402695920737186</v>
+        <v>0.5332354455613233</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.2903726224416396</v>
+        <v>0.5181271639054009</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.3085309339311074</v>
+        <v>0.5130041163479069</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.3529656393479643</v>
+        <v>0.5130041163479069</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4439397021706946</v>
+        <v>0.3930299493754423</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4439397021706946</v>
+        <v>0.3997247332258093</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4280315602895557</v>
+        <v>0.3994782292987803</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4455732469507002</v>
+        <v>0.5205355048390692</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.471550332062447</v>
+        <v>0.5359477187801438</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.471550332062447</v>
+        <v>0.5309392845983958</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4731145247998038</v>
+        <v>0.530554076586069</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4209221242262989</v>
+        <v>0.5453389587167974</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4209221242262989</v>
+        <v>0.551979477635548</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4240264189914607</v>
+        <v>0.5497760294033194</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.41967378745862</v>
+        <v>0.5821366658652654</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4522921215106189</v>
+        <v>0.5786622501988092</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4830673946116626</v>
+        <v>0.5782770421864826</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4856258766341531</v>
+        <v>0.5908728331745131</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4950789250579394</v>
+        <v>0.602267008770965</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4953239689419652</v>
+        <v>0.5258865624455525</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5008706723108685</v>
+        <v>0.5110556889602256</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5008706723108685</v>
+        <v>0.5114793447716347</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5001696083288639</v>
+        <v>0.5154241376256002</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5024115043601751</v>
+        <v>0.5115878746348675</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5015641927373568</v>
+        <v>0.5153163377838689</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5015641927373568</v>
+        <v>0.5157015457961955</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5018106966643858</v>
+        <v>0.4970312458936291</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4988677366510701</v>
+        <v>0.4964688859969222</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4979277122975529</v>
+        <v>0.50636067734315</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4977890082122552</v>
+        <v>0.4957016333987757</v>
       </c>
     </row>
   </sheetData>
